--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 10,68</t>
+          <t>-12,49; 10,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 3,15</t>
+          <t>-12,12; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,32; 9,54</t>
+          <t>-18,57; 10,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 33,51</t>
+          <t>-1,97; 30,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 13,72</t>
+          <t>-14,25; 14,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 3,32</t>
+          <t>-12,16; 1,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 13,77</t>
+          <t>-23,26; 14,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 614,18</t>
+          <t>-29,59; 667,06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 20,17</t>
+          <t>-8,08; 19,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 6,05</t>
+          <t>-12,87; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 10,51</t>
+          <t>-15,15; 11,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 2,68</t>
+          <t>-17,2; 2,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 48,93</t>
+          <t>-15,09; 45,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 7,11</t>
+          <t>-13,6; 6,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 16,98</t>
+          <t>-20,77; 18,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 15,3</t>
+          <t>-69,62; 16,08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 6,37</t>
+          <t>-17,99; 6,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 11,54</t>
+          <t>-6,5; 11,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 19,83</t>
+          <t>-10,12; 19,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 11,02</t>
+          <t>-7,73; 11,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 9,32</t>
+          <t>-22,29; 9,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 14,01</t>
+          <t>-6,79; 13,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 38,86</t>
+          <t>-15,78; 36,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 106,06</t>
+          <t>-42,06; 113,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 10,45</t>
+          <t>-10,45; 10,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 18,63</t>
+          <t>-6,58; 18,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,95; -7,29</t>
+          <t>-38,32; -6,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 0,99</t>
+          <t>-40,11; 0,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 13,58</t>
+          <t>-12,36; 14,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 26,1</t>
+          <t>-7,51; 25,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,89; -9,76</t>
+          <t>-45,6; -9,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 5,13</t>
+          <t>-65,75; 2,64</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 57,39</t>
+          <t>-5,57; 62,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 23,75</t>
+          <t>-10,71; 24,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 3,61</t>
+          <t>-14,85; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 8,07</t>
+          <t>-24,63; 8,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 209,62</t>
+          <t>-9,29; 226,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 33,2</t>
+          <t>-11,35; 34,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 3,76</t>
+          <t>-15,83; 3,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 34,13</t>
+          <t>-59,61; 41,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 13,79</t>
+          <t>-16,63; 14,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 13,91</t>
+          <t>-6,55; 14,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 8,68</t>
+          <t>-31,5; 8,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 6,43</t>
+          <t>-23,02; 5,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 22,59</t>
+          <t>-22,39; 22,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 17,53</t>
+          <t>-7,07; 18,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 14,13</t>
+          <t>-40,06; 11,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,35; 18,63</t>
+          <t>-49,15; 15,2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 20,27</t>
+          <t>-0,58; 18,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 10,46</t>
+          <t>-1,77; 10,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,6</t>
+          <t>-12,16; 7,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 5,16</t>
+          <t>-4,86; 5,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 32,67</t>
+          <t>-0,77; 28,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 12,42</t>
+          <t>-1,94; 12,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 12,63</t>
+          <t>-17,09; 11,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 137,16</t>
+          <t>-52,98; 136,0</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 1,88</t>
+          <t>-20,5; 2,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,52</t>
+          <t>-7,49; 6,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 9,0</t>
+          <t>-2,14; 9,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 7,63</t>
+          <t>-8,9; 7,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 3,85</t>
+          <t>-29,96; 3,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 9,08</t>
+          <t>-8,34; 7,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 10,47</t>
+          <t>-2,18; 11,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 10,05</t>
+          <t>-10,59; 10,17</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,57</t>
+          <t>-3,89; 5,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,38</t>
+          <t>-1,04; 5,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 1,97</t>
+          <t>-6,77; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 1,9</t>
+          <t>-8,75; 1,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 8,48</t>
+          <t>-5,51; 7,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,26</t>
+          <t>-1,15; 5,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,65</t>
+          <t>-8,81; 2,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 6,44</t>
+          <t>-24,71; 5,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 10,98</t>
+          <t>-12,22; 11,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 1,82</t>
+          <t>-11,35; 2,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 10,16</t>
+          <t>-18,53; 10,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 30,57</t>
+          <t>-2,33; 29,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 14,18</t>
+          <t>-13,76; 14,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 1,86</t>
+          <t>-11,58; 2,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 14,35</t>
+          <t>-23,09; 16,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 667,06</t>
+          <t>-34,92; 562,15</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 19,15</t>
+          <t>-9,01; 20,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 6,05</t>
+          <t>-12,41; 6,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 11,74</t>
+          <t>-16,03; 9,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 2,55</t>
+          <t>-16,81; 3,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 45,83</t>
+          <t>-14,99; 50,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 6,97</t>
+          <t>-13,39; 8,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 18,96</t>
+          <t>-21,96; 16,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 16,08</t>
+          <t>-67,39; 22,67</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 6,48</t>
+          <t>-17,43; 7,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 11,63</t>
+          <t>-7,08; 11,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 19,21</t>
+          <t>-9,36; 21,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 11,24</t>
+          <t>-8,38; 11,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 9,39</t>
+          <t>-22,5; 10,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 13,96</t>
+          <t>-7,59; 12,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 36,16</t>
+          <t>-14,13; 42,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 113,99</t>
+          <t>-44,49; 119,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 10,68</t>
+          <t>-11,56; 9,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 18,88</t>
+          <t>-6,13; 19,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,32; -6,41</t>
+          <t>-38,85; -7,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 0,6</t>
+          <t>-38,69; 0,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 14,11</t>
+          <t>-13,79; 13,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 25,92</t>
+          <t>-7,27; 27,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,6; -9,08</t>
+          <t>-48,49; -10,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 2,64</t>
+          <t>-64,02; 2,78</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 62,84</t>
+          <t>-8,17; 56,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 24,21</t>
+          <t>-13,31; 22,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 3,72</t>
+          <t>-14,91; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 8,43</t>
+          <t>-24,66; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 226,49</t>
+          <t>-12,17; 203,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 34,82</t>
+          <t>-13,91; 31,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 3,88</t>
+          <t>-15,03; 3,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 41,35</t>
+          <t>-60,21; 28,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 14,29</t>
+          <t>-15,47; 13,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 14,68</t>
+          <t>-6,16; 14,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 8,16</t>
+          <t>-32,35; 9,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 5,14</t>
+          <t>-25,15; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 22,94</t>
+          <t>-20,48; 21,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 18,07</t>
+          <t>-6,66; 18,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,06; 11,6</t>
+          <t>-39,39; 14,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 15,2</t>
+          <t>-51,71; 16,79</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 18,42</t>
+          <t>0,07; 19,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 10,18</t>
+          <t>-2,63; 9,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 7,27</t>
+          <t>-12,45; 8,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 5,25</t>
+          <t>-5,23; 5,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 28,47</t>
+          <t>0,37; 32,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 12,16</t>
+          <t>-2,85; 11,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 11,68</t>
+          <t>-17,48; 13,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 136,0</t>
+          <t>-59,99; 145,17</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 2,28</t>
+          <t>-20,97; 3,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 6,52</t>
+          <t>-6,35; 6,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 9,88</t>
+          <t>-1,75; 9,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 7,84</t>
+          <t>-8,45; 8,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 3,93</t>
+          <t>-31,42; 5,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 7,7</t>
+          <t>-7,0; 7,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,74</t>
+          <t>-1,86; 10,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 10,17</t>
+          <t>-10,03; 10,83</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,29</t>
+          <t>-4,02; 5,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,12</t>
+          <t>-1,18; 5,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,68</t>
+          <t>-6,67; 1,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,73</t>
+          <t>-8,24; 1,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,88</t>
+          <t>-5,65; 8,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,97</t>
+          <t>-1,35; 6,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,28</t>
+          <t>-8,56; 2,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 5,86</t>
+          <t>-23,78; 5,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>114,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 11,15</t>
+          <t>-12,8; 10,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 2,73</t>
+          <t>-12,02; 3,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 10,52</t>
+          <t>-19,32; 9,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 29,62</t>
+          <t>-5,9; 10,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 14,72</t>
+          <t>-14,22; 13,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 2,94</t>
+          <t>-12,1; 3,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 16,65</t>
+          <t>-23,78; 13,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 562,15</t>
+          <t>-50,59; 216,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,81</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-29,34%</t>
+          <t>-10,45%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 20,36</t>
+          <t>-7,14; 20,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 6,74</t>
+          <t>-12,08; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 9,93</t>
+          <t>-14,84; 10,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 3,71</t>
+          <t>-10,7; 6,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 50,43</t>
+          <t>-13,07; 48,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 8,15</t>
+          <t>-12,96; 7,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 16,21</t>
+          <t>-20,34; 16,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 22,67</t>
+          <t>-44,86; 44,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 7,6</t>
+          <t>-17,94; 6,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 11,0</t>
+          <t>-6,04; 11,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 21,16</t>
+          <t>-11,52; 19,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 11,86</t>
+          <t>-7,49; 11,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 10,69</t>
+          <t>-22,15; 9,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 12,83</t>
+          <t>-6,47; 14,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 42,77</t>
+          <t>-16,73; 38,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 119,32</t>
+          <t>-40,68; 114,45</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,51</t>
+          <t>-15,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,02%</t>
+          <t>-34,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 9,96</t>
+          <t>-11,16; 10,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 19,34</t>
+          <t>-7,08; 18,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; -7,56</t>
+          <t>-38,95; -7,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 0,42</t>
+          <t>-37,81; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 13,78</t>
+          <t>-13,2; 13,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 27,9</t>
+          <t>-7,89; 26,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,49; -10,85</t>
+          <t>-46,89; -9,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 2,78</t>
+          <t>-62,73; 8,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,62</t>
+          <t>-5,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,81%</t>
+          <t>-18,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 56,62</t>
+          <t>-10,35; 57,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 22,7</t>
+          <t>-10,07; 23,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 3,61</t>
+          <t>-13,04; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 7,37</t>
+          <t>-22,55; 9,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 203,98</t>
+          <t>-10,87; 209,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 31,79</t>
+          <t>-11,23; 33,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 3,74</t>
+          <t>-13,2; 3,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 28,48</t>
+          <t>-58,53; 43,96</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,05</t>
+          <t>-10,91</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-24,28%</t>
+          <t>-27,44%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 13,17</t>
+          <t>-17,26; 13,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 14,32</t>
+          <t>-5,97; 13,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 9,62</t>
+          <t>-32,05; 8,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 5,54</t>
+          <t>-24,09; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 21,45</t>
+          <t>-23,0; 22,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 18,06</t>
+          <t>-6,26; 17,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 14,7</t>
+          <t>-38,79; 14,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 16,79</t>
+          <t>-52,17; 17,7</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 19,82</t>
+          <t>1,06; 20,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 9,56</t>
+          <t>-2,29; 10,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 8,64</t>
+          <t>-13,69; 7,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 5,07</t>
+          <t>-4,71; 5,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 32,16</t>
+          <t>1,43; 32,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 11,14</t>
+          <t>-2,46; 12,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 13,67</t>
+          <t>-18,78; 12,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 145,17</t>
+          <t>-54,74; 149,61</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-0,72%</t>
+          <t>-1,68%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 3,07</t>
+          <t>-21,13; 1,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 6,55</t>
+          <t>-6,11; 7,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,36</t>
+          <t>-2,13; 9,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 8,36</t>
+          <t>-9,76; 7,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 5,24</t>
+          <t>-31,88; 3,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 7,81</t>
+          <t>-6,94; 9,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,97</t>
+          <t>-2,28; 10,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 10,83</t>
+          <t>-11,7; 9,72</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-9,88%</t>
+          <t>-8,57%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,44</t>
+          <t>-3,58; 5,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,29</t>
+          <t>-1,15; 5,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,69</t>
+          <t>-6,82; 1,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,77</t>
+          <t>-7,7; 1,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,22</t>
+          <t>-5,07; 8,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,15</t>
+          <t>-1,3; 6,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 2,29</t>
+          <t>-8,78; 2,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 5,78</t>
+          <t>-21,63; 6,09</t>
         </is>
       </c>
     </row>
